--- a/docs/03_詳細設計/05_開発規約/KF-DD-006_開発環境・コーディング規約.xlsx
+++ b/docs/03_詳細設計/05_開発規約/KF-DD-006_開発環境・コーディング規約.xlsx
@@ -13,6 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="構成・命名" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初期ユーザー（開発用）" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実装順序（推奨）" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB変更管理（Flyway）" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git・CI" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docker・環境変数" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -154,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -177,6 +180,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -544,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -556,6 +562,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -564,6 +573,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -598,7 +609,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -629,6 +640,8 @@
       </c>
       <c r="D12" s="10" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -675,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -757,6 +770,29 @@
         </is>
       </c>
       <c r="E3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>DB を Flyway 管理に変更（V1 は編集しない・reset-dev.sql・ddl-auto=validate）、Git・CI・Docker 起動・.env の取り扱いの規約を追加。技術スタックを実装に合わせて訂正（JavaScript／fetch／自作 CSS／Pinia 不使用／JWT 2時間）。初期ユーザーを開発用 100 名・部署 5 件に更新</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -770,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -847,7 +883,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>backend/schema.sql を pgAdmin で手動実行。ddl-auto=validate</t>
+          <t>スキーマは Flyway（db/migration/V*.sql）で管理。ddl-auto=validate。詳細は『DB変更管理（Flyway）』シート</t>
         </is>
       </c>
     </row>
@@ -859,10 +895,14 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>JWT（Spring Security oauth2-jose / Nimbus, HS256, 8時間）＋BCrypt</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
+          <t>JWT（Spring Security oauth2-jose / Nimbus, HS256, 2時間）＋BCrypt</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>パスワードは12文字以上・英字と数字（KF-RD-002 §4）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -872,14 +912,10 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>JavaScriptでも可</t>
-        </is>
-      </c>
+          <t>JavaScript（TypeScript は使わない）</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -889,10 +925,14 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Vue 3（Composition API）＋Vite＋Vue Router＋Pinia</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
+          <t>Vue 3.5（Composition API・&lt;script setup&gt;）＋Vite 7＋Vue Router 4</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>状態管理ライブラリ（Pinia）は使わない</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -902,12 +942,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Element Plus</t>
+          <t>自作 CSS（src/style.css。紺系の配色・共通クラス）</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>画面設計書のコンポーネントに対応</t>
+          <t>UI ライブラリは使わない。KF-BD-012</t>
         </is>
       </c>
     </row>
@@ -919,10 +959,14 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>axios</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
+          <t>fetch（src/api/client.js の共通ラッパー）</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>JWT は localStorage に保存</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -932,12 +976,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>JUnit5 / Vitest</t>
+          <t>JUnit5（バックエンド）</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>テスト設計は後工程</t>
+          <t>現状は起動テストのみ。各 ONL の単体テスト観点のテストコード化は今後。フロントのテストは未導入</t>
         </is>
       </c>
     </row>
@@ -967,7 +1011,58 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>ブランチ：main / feature/*</t>
+          <t>ブランチ：main / feature/*。.gitignore で .env・application-local.properties・target・node_modules を除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>コンテナ</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Docker Compose（postgres:18 / backend / frontend＝nginx）</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>docker compose up -d --build で一式起動。『Docker・環境変数』シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>GitHub Actions（.github/workflows/ci.yml）</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>push / pull request でバックエンドの ./mvnw -B verify とフロントの npm ci &amp;&amp; npm run build を実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Spring Boot Actuator（health のみ公開）</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>docker compose のヘルスチェックが /actuator/health を参照</t>
         </is>
       </c>
     </row>
@@ -983,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1010,7 +1105,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>src/main/java/com/example/kintaiflow/{controller,service,repository,entity,dto,security,exception,batch,config}</t>
+          <t>src/main/java/com/example/kintaiflow/{controller,service,repository,entity,dto,security,exception,batch,config,util}。DB マイグレーションは src/main/resources/db/migration</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1117,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>src/{views,components,router,stores,api,types}。画面は views/SCR-xxx 単位</t>
+          <t>src/{views,components,router,api}。views にページ（LoginView / HomeView / ChangePasswordView）、components に AppLayout など共通部品。画面ID との対応はコメントに SCR-xxx を記載</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1141,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>テーブル・カラム：snake_case（複数形テーブル）。EntityのカラムはsnakeをcamelへJPAで対応付け</t>
+          <t>テーブル・カラム：snake_case（複数形テーブル）。EntityのカラムはsnakeをcamelへJPAで対応付け。マイグレーションファイル：V&lt;連番&gt;__&lt;内容&gt;.sql（例 V2__add_projects.sql）</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1165,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>コンポーネント：UpperCamel／ファイルは画面ID_名称.vue</t>
+          <t>コンポーネント：UpperCamel／ファイルは &lt;名称&gt;View.vue（ページ）、&lt;名称&gt;.vue（部品）。先頭コメントに画面ID・API-ID を記載</t>
         </is>
       </c>
     </row>
@@ -1095,6 +1190,18 @@
       <c r="B9" s="8" t="inlineStr">
         <is>
           <t>1機能1コミット目安。メッセージ：[ONL-005] 申請作成APIを実装</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>秘密情報</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>DB パスワード・JWT 鍵・初期管理者パスワードはソースに書かない。Docker は .env、ローカル起動は application-local.properties（どちらも Git 管理外）に置く</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1124,7 +1231,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>※初期パスワードはアプリ起動時の初期化処理（CommandLineRunner）でBCrypt化して登録する。開発用のみ。本番では使用しない。</t>
+          <t>※開発用の架空ユーザー100名。起動時の初期化処理（DevDataInitializer。CommandLineRunner、@Order(1)）が、users が空かつ KINTAIFLOW_DEV_SEED_PASSWORD（.env の DEV_SEED_PASSWORD）が設定されているときだけ登録する。全員同一のパスワード（BCrypt 化）。本番では使用しない（本番は DEV_SEED_PASSWORD を空にする）。</t>
         </is>
       </c>
     </row>
@@ -1161,116 +1268,203 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>admin@example.com</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>人事 管理者</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>admin@example.com 、adm002@example.com</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>人事 管理者 ほか</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>ADMIN（2名）</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>管理部</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>管理部 10名の内訳：ADMIN 2／MANAGER 1（adm003）／EMPLOYEE 7（adm004〜adm010。上長は adm003）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>manager@example.com</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>manager@example.com 、dev002@example.com</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>佐藤 一郎 ほか</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>MANAGER（2名）</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>システム開発事業部</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>システム開発事業部 30名の内訳：MANAGER 2＋EMPLOYEE 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>taro@example.com 、hanako@example.com</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>山田 太郎、鈴木 花子</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>システム開発事業部</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>佐藤 一郎</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>MANAGER</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>営業部</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>taro@example.com</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>山田 太郎</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>EMPLOYEE</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>営業部</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>佐藤 一郎</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>他に dev005〜dev030@example.com。一般職の上長は番号が偶数なら 1 人目、奇数なら 2 人目の MANAGER</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>hanako@example.com</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>鈴木 花子</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>EMPLOYEE</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>営業部</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>佐藤 一郎</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>sol001〜sol025@example.com</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>（架空氏名）</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>MANAGER 2＋EMPLOYEE 23</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>ソリューション事業部</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>sol001 / sol002</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>25名（sol001・sol002 が上長、sol003〜sol025 が一般職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>sap001〜sap020@example.com</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>（架空氏名）</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>MANAGER 2＋EMPLOYEE 18</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>SAP事業部</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>sap001 / sap002</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>20名</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>cld001〜cld015@example.com</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>（架空氏名）</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>MANAGER 2＋EMPLOYEE 13</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>クラウド基盤サービス部</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>cld001 / cld002</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>15名</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>※合計100名（管理部10／システム開発事業部30／ソリューション事業部25／SAP事業部20／クラウド基盤サービス部15）。部署ID 1〜5 は Flyway V1 が登録する部署マスタに対応。本番の初期管理者は BootstrapAdminInitializer が別途1名作成する（『Docker・環境変数』シート）。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1315,12 +1509,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>プロジェクト作成・DB接続・schema.sql投入</t>
+          <t>プロジェクト作成・DB接続・Flyway によるスキーマ作成（V1__init_schema.sql）</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>KF-DD-003</t>
+          <t>KF-DD-003, KF-DD-006</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1524,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>認証（ログイン・JWT・ロール制御）</t>
+          <t>認証（ログイン・JWT・ロール制御・アカウントロック）とパスワード変更</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>ONL-001</t>
+          <t>ONL-001, ONL-023, SCR-001/007</t>
         </is>
       </c>
     </row>
@@ -1426,6 +1620,400 @@
       <c r="C9" s="8" t="inlineStr">
         <is>
           <t>ONL-019, BAT-001〜003</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>方式</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>スキーマは Flyway で管理する（backend/src/main/resources/db/migration/V&lt;連番&gt;__&lt;内容&gt;.sql）。アプリ起動時に未適用のファイルを順に自動適用する。旧 schema.sql（手動実行）は廃止</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>V1 の扱い</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql（初期スキーマ。users の失敗回数・ロック・パスワード変更要否・変更日時の 4 列、部署マスタ 5 件、休暇種別マスタを含む）は一度適用したら編集しない。Flyway がチェックサムを検証するため、編集すると起動に失敗する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>変更の追加</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>テーブル・列・索引の変更は新しいファイルを追加する（例：V2__add_projects.sql）。適用済みのファイルは書き換えない。変更を入れたら対応するテーブル設計書（KF-DD-003 / TBL-xx）と ONL を同じ版で更新する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>JPA との関係</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>spring.jpa.hibernate.ddl-auto=validate。Entity と DB 定義がずれていると起動時に失敗する（本番も同じ）。ddl-auto=update / create は使わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>既存の開発 DB</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>旧 schema.sql で作った DB は spring.flyway.baseline-on-migrate=true・baseline-version=1 により V1 適用済みとして引き継ぐ。ただし V1 に含まれる新しい列（users の 4 列など）は追加されないため、そのままでは validate で失敗する。backend/db/reset-dev.sql で作り直すこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>開発 DB の作り直し</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>backend/db/reset-dev.sql を実行する（DROP SCHEMA public CASCADE; CREATE SCHEMA public;）。全テーブルと Flyway 履歴が消える。実行後にバックエンドを起動すると V1 から作り直し、DEV_SEED_PASSWORD が設定されていれば開発用ユーザー100名が投入される。本番では絶対に実行しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>データの初期投入</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>部署マスタ（管理部／システム開発事業部／ソリューション事業部／SAP事業部／クラウド基盤サービス部＝ID 1〜5）と休暇種別マスタ（法定 11 種）は V1 に含む。ユーザーは V1 に含めず、アプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>タイムゾーン</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>DB セッションは spring.datasource.hikari.connection-init-sql で Asia/Tokyo に固定。updated_at は DB トリガ（set_updated_at）で更新</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>ブランチ</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>main（常に動く状態）と feature/*。1 機能ごとに feature ブランチを切り、レビュー後に main へ取り込む</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>コミット</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>1 機能 1 コミットを目安。メッセージの先頭に処理ID：[ONL-005] 申請作成APIを実装。設計書とコードを同じコミット（または同じ PR）で更新する</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Git に入れないもの</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>秘密情報とローカル設定・生成物：.env、application-local.properties、target/、node_modules/、dist/、.idea/、*.iml（.gitignore 済み）。.env.example（値は雛形）は入れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>GitHub Actions（.github/workflows/ci.yml）。push と pull request のたびに自動実行する。backend ジョブ：Java 21（Temurin）で ./mvnw -B verify。frontend ジョブ：Node 24 で npm ci と npm run build</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>CI の範囲</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>現在はビルドとテストのみ。脆弱性検査、検証環境への自動配置、本番の承認付き配置は未実装（KF-RD-002 §5 の今後の課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>マージ条件</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>CI が成功していること（運用ルール。ブランチ保護の設定は別途）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>起動</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>docker compose up -d --build（リポジトリ直下の docker-compose.yml）。停止は docker compose down（データは volume dbdata に残る）。ブラウザで http://localhost:8081 を開く（WEB_PORT で変更）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>構成</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>db：postgres:18（TZ=Asia/Tokyo、pg_isready のヘルスチェック）／backend：./backend の Dockerfile からビルド（/actuator/health のヘルスチェック。db が healthy になってから起動）／frontend：./frontend の Dockerfile から nginx で配信（backend へ同一オリジンでプロキシ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>設定の渡し方</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>リポジトリ直下に .env を作成する（.env.example をコピーして値を入れる。.env は Git に入れない）。docker-compose.yml が環境変数としてコンテナへ渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>DB_PASSWORD</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>PostgreSQL のパスワード（必須）。長くランダムなものにする。未設定だと compose が起動を止める</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>JWT_SECRET</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>JWT 署名鍵（必須）。32バイト以上の乱数を base64 にしたもの。アプリ側の設定名は KINTAIFLOW_JWT_SECRET</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>DEV_SEED_PASSWORD</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>開発用ダミーユーザー100名の共通パスワード。設定したときだけ DevDataInitializer が登録する。本番では空欄にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>BOOTSTRAP_ADMIN_EMAIL / BOOTSTRAP_ADMIN_PASSWORD</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>本番の初回起動用。users が 0 件のときだけ、この ADMIN を 1 名作成する（BootstrapAdminInitializer）。パスワードは 12 文字以上・英字と数字（違反すると起動失敗）。初回ログイン時に変更を求められる（must_change_password=true）。ログにはメールアドレスのみ出力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>WEB_PORT</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>公開ポート（既定 8081）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>ローカル起動（Docker なし）</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>バックエンド：backend で ./mvnw spring-boot:run（DB パスワード等は Git 管理外の application-local.properties）。フロント：frontend で npm run dev（http://localhost:5173。CORS は kintaiflow.cors.allowed-origins で許可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>環境の分離</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>開発／検証／本番ごとに .env を別に用意し、本番データを開発に持ち込まない（KF-RD-002 §5）。現状は開発環境のみ構築済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>バックアップ</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>本番はマネージド PostgreSQL の自動日次バックアップを使う想定（KF-BD-010）。compose 構成の volume は開発・検証用で、バックアップ機能は持たない</t>
         </is>
       </c>
     </row>
